--- a/温度阻值标定.xlsx
+++ b/温度阻值标定.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="18580" windowHeight="9880"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>阻值</t>
   </si>
@@ -41,6 +41,39 @@
   </si>
   <si>
     <t>ADC采集1</t>
+  </si>
+  <si>
+    <t>PT100-V2</t>
+  </si>
+  <si>
+    <t>使用简单线性拟合R-&gt;T</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>GD_V</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>GD_R</t>
+  </si>
+  <si>
+    <t>GD_T</t>
+  </si>
+  <si>
+    <t>delta_R</t>
+  </si>
+  <si>
+    <t>delta_T</t>
+  </si>
+  <si>
+    <t>最大误差</t>
+  </si>
+  <si>
+    <t>平均误差</t>
   </si>
 </sst>
 </file>
@@ -206,7 +239,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -215,6 +248,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -400,12 +445,100 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="17">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -532,7 +665,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -544,120 +677,150 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="13">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="14">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -971,10 +1134,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <cols>
+    <col min="3" max="5" width="11.7272727272727"/>
+    <col min="6" max="7" width="12.8181818181818"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -988,7 +1155,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>0</v>
       </c>
@@ -999,9 +1166,9 @@
         <v>0.015</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:6">
       <c r="A3">
-        <v>81.7</v>
+        <v>81.76</v>
       </c>
       <c r="B3">
         <v>1.74</v>
@@ -1013,9 +1180,9 @@
         <v>1.755</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:6">
       <c r="A4">
-        <v>82.3</v>
+        <v>82.4</v>
       </c>
       <c r="B4">
         <v>1.75</v>
@@ -1027,7 +1194,7 @@
         <v>1.779</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>100.1</v>
       </c>
@@ -1041,9 +1208,9 @@
         <v>2.146</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:6">
       <c r="A6">
-        <v>106.7</v>
+        <v>106.88</v>
       </c>
       <c r="B6">
         <v>2.27</v>
@@ -1055,9 +1222,9 @@
         <v>2.285</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:6">
       <c r="A7">
-        <v>110.7</v>
+        <v>110.66</v>
       </c>
       <c r="B7">
         <v>2.35</v>
@@ -1069,7 +1236,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>112.6</v>
       </c>
@@ -1083,9 +1250,9 @@
         <v>2.398</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:6">
       <c r="A9">
-        <v>123</v>
+        <v>122.9</v>
       </c>
       <c r="B9">
         <v>2.62</v>
@@ -1097,7 +1264,7 @@
         <v>2.631</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>130.9</v>
       </c>
@@ -1111,9 +1278,9 @@
         <v>2.814</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:6">
       <c r="A11">
-        <v>138.9</v>
+        <v>138.85</v>
       </c>
       <c r="B11">
         <v>3</v>
@@ -1125,7 +1292,7 @@
         <v>2.964</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>150.2</v>
       </c>
@@ -1139,9 +1306,9 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:6">
       <c r="A13">
-        <v>160.1</v>
+        <v>160.15</v>
       </c>
       <c r="B13">
         <v>3.4</v>
@@ -1151,6 +1318,349 @@
       </c>
       <c r="D13">
         <v>3.425</v>
+      </c>
+    </row>
+    <row r="16" ht="14.75" spans="1:6">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" ht="15.5" spans="1:7">
+      <c r="A17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" ht="14.75" spans="1:7">
+      <c r="A18" s="1">
+        <v>0</v>
+      </c>
+      <c r="B18"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="6"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="1">
+        <v>81.76</v>
+      </c>
+      <c r="B19">
+        <v>1.71025</v>
+      </c>
+      <c r="C19" s="2">
+        <v>-46.352433</v>
+      </c>
+      <c r="D19" s="1">
+        <v>81.773705</v>
+      </c>
+      <c r="E19" s="2">
+        <v>-47.334263</v>
+      </c>
+      <c r="F19" s="5">
+        <f>ABS(D19-A19)</f>
+        <v>0.0137050000000016</v>
+      </c>
+      <c r="G19" s="6">
+        <f>ABS(E19-C19)</f>
+        <v>0.981830000000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="1">
+        <v>82.4</v>
+      </c>
+      <c r="B20">
+        <v>1.7225</v>
+      </c>
+      <c r="C20" s="2">
+        <v>-44.73664</v>
+      </c>
+      <c r="D20" s="1">
+        <v>82.353561</v>
+      </c>
+      <c r="E20" s="2">
+        <v>-45.828358</v>
+      </c>
+      <c r="F20" s="5">
+        <f t="shared" ref="F20:F29" si="0">ABS(D20-A20)</f>
+        <v>0.0464390000000066</v>
+      </c>
+      <c r="G20" s="6">
+        <f t="shared" ref="G20:G29" si="1">ABS(E20-C20)</f>
+        <v>1.091718</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="1">
+        <v>100.1</v>
+      </c>
+      <c r="B21">
+        <v>2.092875</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0.255875</v>
+      </c>
+      <c r="D21" s="1">
+        <v>100.072067</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0.187161</v>
+      </c>
+      <c r="F21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.0279329999999902</v>
+      </c>
+      <c r="G21" s="6">
+        <f t="shared" si="1"/>
+        <v>0.068714</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="1">
+        <v>106.88</v>
+      </c>
+      <c r="B22">
+        <v>2.2355</v>
+      </c>
+      <c r="C22" s="2">
+        <v>17.649104</v>
+      </c>
+      <c r="D22" s="1">
+        <v>106.898834</v>
+      </c>
+      <c r="E22" s="2">
+        <v>17.900976</v>
+      </c>
+      <c r="F22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.0188339999999982</v>
+      </c>
+      <c r="G22" s="6">
+        <f t="shared" si="1"/>
+        <v>0.251871999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="1">
+        <v>110.66</v>
+      </c>
+      <c r="B23">
+        <v>2.314125</v>
+      </c>
+      <c r="C23" s="2">
+        <v>27.384499</v>
+      </c>
+      <c r="D23" s="1">
+        <v>110.658936</v>
+      </c>
+      <c r="E23" s="2">
+        <v>27.666079</v>
+      </c>
+      <c r="F23" s="5">
+        <f t="shared" si="0"/>
+        <v>0.00106399999999951</v>
+      </c>
+      <c r="G23" s="6">
+        <f t="shared" si="1"/>
+        <v>0.281579999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="1">
+        <v>112.6</v>
+      </c>
+      <c r="B24">
+        <v>2.35425</v>
+      </c>
+      <c r="C24" s="2">
+        <v>32.391657</v>
+      </c>
+      <c r="D24" s="1">
+        <v>112.57785</v>
+      </c>
+      <c r="E24" s="2">
+        <v>32.665073</v>
+      </c>
+      <c r="F24" s="5">
+        <f t="shared" si="0"/>
+        <v>0.0221499999999963</v>
+      </c>
+      <c r="G24" s="6">
+        <f t="shared" si="1"/>
+        <v>0.273415999999997</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="1">
+        <v>122.9</v>
+      </c>
+      <c r="B25">
+        <v>2.57125</v>
+      </c>
+      <c r="C25" s="2">
+        <v>59.100326</v>
+      </c>
+      <c r="D25" s="1">
+        <v>122.949509</v>
+      </c>
+      <c r="E25" s="2">
+        <v>59.600597</v>
+      </c>
+      <c r="F25" s="5">
+        <f t="shared" si="0"/>
+        <v>0.0495090000000005</v>
+      </c>
+      <c r="G25" s="6">
+        <f t="shared" si="1"/>
+        <v>0.500270999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="1">
+        <v>130.9</v>
+      </c>
+      <c r="B26">
+        <v>2.737625</v>
+      </c>
+      <c r="C26" s="2">
+        <v>79.99716</v>
+      </c>
+      <c r="D26" s="1">
+        <v>130.912079</v>
+      </c>
+      <c r="E26" s="2">
+        <v>80.279648</v>
+      </c>
+      <c r="F26" s="5">
+        <f t="shared" si="0"/>
+        <v>0.012079</v>
+      </c>
+      <c r="G26" s="6">
+        <f t="shared" si="1"/>
+        <v>0.282488000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="1">
+        <v>138.85</v>
+      </c>
+      <c r="B27">
+        <v>2.904375</v>
+      </c>
+      <c r="C27" s="2">
+        <v>100.909457</v>
+      </c>
+      <c r="D27" s="1">
+        <v>138.88063</v>
+      </c>
+      <c r="E27" s="2">
+        <v>100.974228</v>
+      </c>
+      <c r="F27" s="5">
+        <f t="shared" si="0"/>
+        <v>0.0306300000000022</v>
+      </c>
+      <c r="G27" s="6">
+        <f t="shared" si="1"/>
+        <v>0.0647709999999933</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="1">
+        <v>150.2</v>
+      </c>
+      <c r="B28">
+        <v>3.139625</v>
+      </c>
+      <c r="C28" s="2">
+        <v>131.057392</v>
+      </c>
+      <c r="D28" s="1">
+        <v>150.143005</v>
+      </c>
+      <c r="E28" s="2">
+        <v>130.222961</v>
+      </c>
+      <c r="F28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.0569950000000006</v>
+      </c>
+      <c r="G28" s="6">
+        <f t="shared" si="1"/>
+        <v>0.834430999999995</v>
+      </c>
+    </row>
+    <row r="29" ht="14.75" spans="1:7">
+      <c r="A29" s="1">
+        <v>160.15</v>
+      </c>
+      <c r="B29">
+        <v>3.349</v>
+      </c>
+      <c r="C29" s="2">
+        <v>157.827231</v>
+      </c>
+      <c r="D29" s="1">
+        <v>160.150009</v>
+      </c>
+      <c r="E29" s="2">
+        <v>156.211472</v>
+      </c>
+      <c r="F29" s="5">
+        <f t="shared" si="0"/>
+        <v>9.00000000569889e-6</v>
+      </c>
+      <c r="G29" s="6">
+        <f t="shared" si="1"/>
+        <v>1.61575900000003</v>
+      </c>
+    </row>
+    <row r="30" ht="14.75" spans="1:7">
+      <c r="E30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="7">
+        <f>MAX(F19:F29)</f>
+        <v>0.0569950000000006</v>
+      </c>
+      <c r="G30" s="8">
+        <f>MAX(G19:G29)</f>
+        <v>1.61575900000003</v>
+      </c>
+    </row>
+    <row r="31" ht="14.75" spans="1:7">
+      <c r="E31" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31" s="9">
+        <f>AVERAGE(F19:F29)</f>
+        <v>0.0253951818181819</v>
+      </c>
+      <c r="G31" s="10">
+        <f>AVERAGE(G19:G29)</f>
+        <v>0.567895454545455</v>
       </c>
     </row>
   </sheetData>
